--- a/VII sem/OBiP/lab01/Статистика обзор.xlsx
+++ b/VII sem/OBiP/lab01/Статистика обзор.xlsx
@@ -1,25 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Институт\Экономика ERP\Лабораторная работа 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\BGTU\VII sem\OBiP\9BA01_A5B5B7B7B8_B7B0BFBEBBBDB5BDBD8BB5_B4BEBA83BCB5BD828B\ЛР1_Хеззи\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F929C5D9-D80A-4780-94D3-F3FBB44A1711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20633" windowHeight="7598" activeTab="2"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Число зарегистрированных" sheetId="1" r:id="rId1"/>
     <sheet name="Организационно-правовые формы" sheetId="2" r:id="rId2"/>
     <sheet name="Формы регистрации" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -28,12 +38,21 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="34">
   <si>
+    <t>Число зарегистрированных субъектов хозяйствования итого</t>
+  </si>
+  <si>
     <t>ЮЛ</t>
   </si>
   <si>
     <t>ИП</t>
   </si>
   <si>
+    <t>2022/2021, %</t>
+  </si>
+  <si>
+    <t>2023/2022, %</t>
+  </si>
+  <si>
     <t>Всего РБ</t>
   </si>
   <si>
@@ -49,24 +68,15 @@
     <t>Гродненская область</t>
   </si>
   <si>
+    <t>Минская область</t>
+  </si>
+  <si>
+    <t>Могилевская область</t>
+  </si>
+  <si>
     <t>Минск</t>
   </si>
   <si>
-    <t>Минская область</t>
-  </si>
-  <si>
-    <t>Могилевская область</t>
-  </si>
-  <si>
-    <t>2022/2021, %</t>
-  </si>
-  <si>
-    <t>2023/2022, %</t>
-  </si>
-  <si>
-    <t>Число зарегистрированных субъектов хозяйствования итого</t>
-  </si>
-  <si>
     <t>Число зарегистрированных юридических лиц по организационно-правовым формам</t>
   </si>
   <si>
@@ -82,28 +92,28 @@
     <t xml:space="preserve">УП </t>
   </si>
   <si>
+    <t>ЗАО и ОАО</t>
+  </si>
+  <si>
+    <t>Учреждения</t>
+  </si>
+  <si>
+    <t>КФХ</t>
+  </si>
+  <si>
     <t>Иные</t>
   </si>
   <si>
-    <t>КФХ</t>
-  </si>
-  <si>
-    <t>ЗАО и ОАО</t>
-  </si>
-  <si>
-    <t>Учреждения</t>
-  </si>
-  <si>
     <t>Согласование наименований ЮЛ</t>
   </si>
   <si>
+    <t>2023/2015, %</t>
+  </si>
+  <si>
     <t>В бумажном виде</t>
   </si>
   <si>
     <t>В электронном виде</t>
-  </si>
-  <si>
-    <t>2023/2015, %</t>
   </si>
   <si>
     <t>Электронная регистрация и ликвидация субъектов хозяйствования</t>
@@ -133,33 +143,35 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -170,7 +182,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -230,11 +242,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -243,9 +279,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -253,6 +301,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -276,6 +327,1798 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Юридические лица</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>2022/2021</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Число зарегистрированных'!$B$3:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9708</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>759</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>586</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>687</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>596</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1595</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>586</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4851</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Число зарегистрированных'!$C$3:$C$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9831</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>768</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>621</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>649</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>594</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1529</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>542</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5101</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E3F0-4BB7-9405-476406E8A042}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>2023/2021</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Число зарегистрированных'!$B$3:$B$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9708</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>759</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>586</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>687</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>596</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1595</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>586</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4851</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Число зарегистрированных'!$D$3:$D$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12137</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>767</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>827</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>754</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1776</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>741</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6277</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E3F0-4BB7-9405-476406E8A042}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Индивидуальные предприниматели</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>2022/2021</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Число зарегистрированных'!$G$3:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29070</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4270</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2905</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3661</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3841</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5433</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3055</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5905</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Число зарегистрированных'!$H$3:$H$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15498</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2805</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2332</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2354</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2031</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A063-44A3-BE7E-42817FA3EE5C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>2023/2021</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Число зарегистрированных'!$G$3:$G$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>29070</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4270</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2905</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3661</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3841</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5433</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3055</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>5905</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Число зарегистрированных'!$I$3:$I$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>15939</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3072</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1896</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2358</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2204</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4441</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1968</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-A063-44A3-BE7E-42817FA3EE5C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Юридические лица по формам</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>2021</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Организационно-правовые формы'!$A$2:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Формы</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ООО</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ОДО</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>УП </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ЗАО и ОАО</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Учреждения</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>КФХ</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Иные</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Организационно-правовые формы'!$B$2:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7968</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>856</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>309</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>395</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B6FB-4FF5-8BC1-79CEEC34146F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>2022</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Организационно-правовые формы'!$A$2:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Формы</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ООО</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ОДО</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>УП </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ЗАО и ОАО</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Учреждения</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>КФХ</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Иные</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Организационно-правовые формы'!$C$2:$C$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8113</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>362</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B6FB-4FF5-8BC1-79CEEC34146F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>2023</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Организационно-правовые формы'!$A$2:$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>Формы</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>ООО</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>ОДО</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>УП </c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>ЗАО и ОАО</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Учреждения</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>КФХ</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Иные</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Организационно-правовые формы'!$D$2:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>2023</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10346</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1159</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>306</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B6FB-4FF5-8BC1-79CEEC34146F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Согласование наименований</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>2015</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$A$2:$A$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$A$3:$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>В бумажном виде</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>В электронном виде</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$B$2:$B$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$B$3:$B$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>14167</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10670</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B4D2-4680-8DFE-B070087E73DE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>2021</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$A$2:$A$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$A$3:$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>В бумажном виде</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>В электронном виде</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$C$2:$C$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$C$3:$C$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2293</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>25476</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B4D2-4680-8DFE-B070087E73DE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>2022</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$A$2:$A$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$A$3:$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>В бумажном виде</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>В электронном виде</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$D$2:$D$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$D$3:$D$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>3127</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33359</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B4D2-4680-8DFE-B070087E73DE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>2023</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$A$2:$A$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$A$3:$A$4</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>В бумажном виде</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>В электронном виде</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$E$2:$E$4</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$E$3:$E$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>2718</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>31316</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-B4D2-4680-8DFE-B070087E73DE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Электронная регистрация и ликвидация</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>2021</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$A$8:$A$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$A$9:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Регистрация ЮЛ, в т.ч. изменений</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Регистрация ИП, в т.ч. изменений</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Уведомления</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Ликвидация ЮЛ, ИП</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$B$8:$B$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$B$9:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>3811</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>875</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5419</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1435</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9609-42C3-A4CC-C4A2F2B3635E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>2022</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$A$8:$A$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$A$9:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Регистрация ЮЛ, в т.ч. изменений</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Регистрация ИП, в т.ч. изменений</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Уведомления</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Ликвидация ЮЛ, ИП</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$C$8:$C$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$C$9:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>868</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6221</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1878</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9609-42C3-A4CC-C4A2F2B3635E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>2023</c:v>
+          </c:tx>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$A$8:$A$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$A$9:$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Регистрация ЮЛ, в т.ч. изменений</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Регистрация ИП, в т.ч. изменений</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Уведомления</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Ликвидация ЮЛ, ИП</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>'Формы регистрации'!$D$8:$D$12</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>'Формы регистрации'!$D$9:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>4439</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>692</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7416</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1493</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9609-42C3-A4CC-C4A2F2B3635E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48650112"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -319,76 +2162,16 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -400,23 +2183,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -426,23 +2209,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -450,26 +2233,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -504,17 +2284,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -531,47 +2311,42 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.296875" customWidth="1"/>
-    <col min="5" max="5" width="12.3984375" customWidth="1"/>
-    <col min="6" max="6" width="12.296875" customWidth="1"/>
-    <col min="10" max="10" width="12.3984375" customWidth="1"/>
-    <col min="11" max="11" width="11.796875" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="12.44140625" customWidth="1"/>
+    <col min="11" max="11" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
-      <c r="B2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="6" t="s">
+      <c r="B2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="11"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="22"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
@@ -585,10 +2360,10 @@
         <v>2023</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G3" s="3">
         <v>2021</v>
@@ -600,131 +2375,323 @@
         <v>2023</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="B4" s="15">
+        <v>9708</v>
+      </c>
+      <c r="C4" s="15">
+        <v>9831</v>
+      </c>
+      <c r="D4" s="15">
+        <v>12137</v>
+      </c>
+      <c r="E4" s="2">
+        <f>(C4/B4)*100</f>
+        <v>101.26699629171819</v>
+      </c>
+      <c r="F4" s="2">
+        <f>(D4/C4)*100</f>
+        <v>123.45641338622724</v>
+      </c>
+      <c r="G4" s="16">
+        <v>29070</v>
+      </c>
+      <c r="H4" s="16">
+        <v>15498</v>
+      </c>
+      <c r="I4" s="16">
+        <v>15939</v>
+      </c>
+      <c r="J4" s="2">
+        <f>(H4/G4)*100</f>
+        <v>53.312693498452013</v>
+      </c>
+      <c r="K4" s="2">
+        <f>(I4/H4)*100</f>
+        <v>102.84552845528457</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="B5" s="2">
+        <v>759</v>
+      </c>
+      <c r="C5" s="13">
+        <v>768</v>
+      </c>
+      <c r="D5" s="13">
+        <v>970</v>
+      </c>
+      <c r="E5" s="16">
+        <f t="shared" ref="E5:E11" si="0">(C5/B5)*100</f>
+        <v>101.18577075098814</v>
+      </c>
+      <c r="F5" s="16">
+        <f t="shared" ref="F5:F11" si="1">(D5/C5)*100</f>
+        <v>126.30208333333333</v>
+      </c>
+      <c r="G5" s="14">
+        <v>4270</v>
+      </c>
+      <c r="H5" s="14">
+        <v>2805</v>
+      </c>
+      <c r="I5" s="14">
+        <v>3072</v>
+      </c>
+      <c r="J5" s="16">
+        <f t="shared" ref="J5:J11" si="2">(H5/G5)*100</f>
+        <v>65.69086651053864</v>
+      </c>
+      <c r="K5" s="16">
+        <f t="shared" ref="K5:K11" si="3">(I5/H5)*100</f>
+        <v>109.5187165775401</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="B6" s="12">
+        <v>586</v>
+      </c>
+      <c r="C6" s="13">
+        <v>621</v>
+      </c>
+      <c r="D6" s="13">
+        <v>767</v>
+      </c>
+      <c r="E6" s="16">
+        <f t="shared" si="0"/>
+        <v>105.97269624573377</v>
+      </c>
+      <c r="F6" s="16">
+        <f t="shared" si="1"/>
+        <v>123.51046698872786</v>
+      </c>
+      <c r="G6" s="14">
+        <v>2905</v>
+      </c>
+      <c r="H6" s="14">
+        <v>1975</v>
+      </c>
+      <c r="I6" s="14">
+        <v>1896</v>
+      </c>
+      <c r="J6" s="16">
+        <f t="shared" si="2"/>
+        <v>67.986230636833042</v>
+      </c>
+      <c r="K6" s="16">
+        <f t="shared" si="3"/>
+        <v>96</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="B7" s="12">
+        <v>687</v>
+      </c>
+      <c r="C7" s="13">
+        <v>649</v>
+      </c>
+      <c r="D7" s="13">
+        <v>827</v>
+      </c>
+      <c r="E7" s="16">
+        <f t="shared" si="0"/>
+        <v>94.468704512372639</v>
+      </c>
+      <c r="F7" s="16">
+        <f t="shared" si="1"/>
+        <v>127.42681047765794</v>
+      </c>
+      <c r="G7" s="14">
+        <v>3661</v>
+      </c>
+      <c r="H7" s="14">
+        <v>2332</v>
+      </c>
+      <c r="I7" s="14">
+        <v>2358</v>
+      </c>
+      <c r="J7" s="16">
+        <f t="shared" si="2"/>
+        <v>63.698443048347443</v>
+      </c>
+      <c r="K7" s="16">
+        <f t="shared" si="3"/>
+        <v>101.11492281303602</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="B8" s="12">
+        <v>596</v>
+      </c>
+      <c r="C8" s="13">
+        <v>594</v>
+      </c>
+      <c r="D8" s="13">
+        <v>754</v>
+      </c>
+      <c r="E8" s="16">
+        <f t="shared" si="0"/>
+        <v>99.664429530201332</v>
+      </c>
+      <c r="F8" s="16">
+        <f t="shared" si="1"/>
+        <v>126.93602693602695</v>
+      </c>
+      <c r="G8" s="14">
+        <v>3841</v>
+      </c>
+      <c r="H8" s="14">
+        <v>2354</v>
+      </c>
+      <c r="I8" s="14">
+        <v>2204</v>
+      </c>
+      <c r="J8" s="16">
+        <f t="shared" si="2"/>
+        <v>61.286123405363192</v>
+      </c>
+      <c r="K8" s="16">
+        <f t="shared" si="3"/>
+        <v>93.62786745964317</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="B9" s="12">
+        <v>1595</v>
+      </c>
+      <c r="C9" s="13">
+        <v>1529</v>
+      </c>
+      <c r="D9" s="13">
+        <v>1776</v>
+      </c>
+      <c r="E9" s="16">
+        <f t="shared" si="0"/>
+        <v>95.862068965517238</v>
+      </c>
+      <c r="F9" s="16">
+        <f t="shared" si="1"/>
+        <v>116.15434924787442</v>
+      </c>
+      <c r="G9" s="14">
+        <v>5433</v>
+      </c>
+      <c r="H9" s="14">
+        <v>4001</v>
+      </c>
+      <c r="I9" s="14">
+        <v>4441</v>
+      </c>
+      <c r="J9" s="16">
+        <f t="shared" si="2"/>
+        <v>73.64255475796061</v>
+      </c>
+      <c r="K9" s="16">
+        <f t="shared" si="3"/>
+        <v>110.99725068732818</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="B10" s="12">
+        <v>586</v>
+      </c>
+      <c r="C10" s="13">
+        <v>542</v>
+      </c>
+      <c r="D10" s="13">
+        <v>741</v>
+      </c>
+      <c r="E10" s="16">
+        <f t="shared" si="0"/>
+        <v>92.491467576791806</v>
+      </c>
+      <c r="F10" s="16">
+        <f t="shared" si="1"/>
+        <v>136.71586715867159</v>
+      </c>
+      <c r="G10" s="14">
+        <v>3055</v>
+      </c>
+      <c r="H10" s="14">
+        <v>2031</v>
+      </c>
+      <c r="I10" s="14">
+        <v>1968</v>
+      </c>
+      <c r="J10" s="16">
+        <f t="shared" si="2"/>
+        <v>66.481178396072011</v>
+      </c>
+      <c r="K10" s="16">
+        <f t="shared" si="3"/>
+        <v>96.898079763663219</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B11" s="12">
+        <v>4851</v>
+      </c>
+      <c r="C11" s="13">
+        <v>5101</v>
+      </c>
+      <c r="D11" s="13">
+        <v>6277</v>
+      </c>
+      <c r="E11" s="16">
+        <f t="shared" si="0"/>
+        <v>105.15357658214801</v>
+      </c>
+      <c r="F11" s="16">
+        <f t="shared" si="1"/>
+        <v>123.05430307782788</v>
+      </c>
+      <c r="G11" s="2">
+        <v>5905</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0</v>
+      </c>
+      <c r="I11" s="2">
+        <v>0</v>
+      </c>
+      <c r="J11" s="16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K11" s="16" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -732,18 +2699,18 @@
     <mergeCell ref="G2:K2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
-    <col min="5" max="5" width="12.19921875" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -765,152 +2732,275 @@
         <v>2023</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="B3" s="2">
+        <v>7968</v>
+      </c>
+      <c r="C3" s="2">
+        <v>8113</v>
+      </c>
+      <c r="D3" s="2">
+        <v>10346</v>
+      </c>
+      <c r="E3" s="2">
+        <f>(C3/B3)*100</f>
+        <v>101.81977911646587</v>
+      </c>
+      <c r="F3" s="2">
+        <f>(D3/C3)*100</f>
+        <v>127.52372735116479</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
+      <c r="B4" s="2">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" ref="E4:E9" si="0">(C4/B4)*100</f>
+        <v>200</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" ref="F4:F9" si="1">(D4/C4)*100</f>
+        <v>200</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
+      <c r="B5" s="2">
+        <v>856</v>
+      </c>
+      <c r="C5" s="2">
+        <v>950</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1159</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>110.98130841121497</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="1"/>
+        <v>122</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="B6" s="2">
+        <v>47</v>
+      </c>
+      <c r="C6" s="2">
+        <v>29</v>
+      </c>
+      <c r="D6" s="2">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
+        <v>61.702127659574465</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="1"/>
+        <v>120.68965517241379</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="B7" s="2">
+        <v>130</v>
+      </c>
+      <c r="C7" s="2">
+        <v>86</v>
+      </c>
+      <c r="D7" s="2">
+        <v>69</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
+        <v>66.153846153846146</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="1"/>
+        <v>80.232558139534888</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="B8" s="2">
+        <v>309</v>
+      </c>
+      <c r="C8" s="2">
+        <v>285</v>
+      </c>
+      <c r="D8" s="2">
+        <v>210</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="0"/>
+        <v>92.233009708737868</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="1"/>
+        <v>73.68421052631578</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B9" s="2">
+        <v>395</v>
+      </c>
+      <c r="C9" s="2">
+        <v>362</v>
+      </c>
+      <c r="D9" s="2">
+        <v>306</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="0"/>
+        <v>91.64556962025317</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="1"/>
+        <v>84.530386740331494</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H18"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.5" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="12.3984375" customWidth="1"/>
-    <col min="7" max="7" width="12.5" customWidth="1"/>
+    <col min="6" max="8" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="3">
+        <v>2015</v>
+      </c>
+      <c r="C2" s="6">
         <v>2021</v>
       </c>
-      <c r="C2" s="3">
+      <c r="D2" s="7">
         <v>2022</v>
       </c>
-      <c r="D2" s="3">
+      <c r="E2" s="7">
         <v>2023</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2">
+        <v>14167</v>
+      </c>
+      <c r="C3" s="9">
+        <v>2293</v>
+      </c>
+      <c r="D3" s="10">
+        <v>3127</v>
+      </c>
+      <c r="E3" s="10">
+        <v>2718</v>
+      </c>
+      <c r="F3" s="10">
+        <f>(D3/C3)*100</f>
+        <v>136.37156563453991</v>
+      </c>
+      <c r="G3" s="10">
+        <f>(E3/D3)*100</f>
+        <v>86.920370962583945</v>
+      </c>
+      <c r="H3" s="10">
+        <f>(E3/B3)*100</f>
+        <v>19.185430931036919</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>10670</v>
+      </c>
+      <c r="C4" s="9">
+        <v>25476</v>
+      </c>
+      <c r="D4" s="10">
+        <v>33359</v>
+      </c>
+      <c r="E4" s="10">
+        <v>31316</v>
+      </c>
+      <c r="F4" s="10">
+        <f>(D4/C4)*100</f>
+        <v>130.94284817082743</v>
+      </c>
+      <c r="G4" s="10">
+        <f>(E4/D4)*100</f>
+        <v>93.875715698911833</v>
+      </c>
+      <c r="H4" s="10">
+        <f>(E4/B4)*100</f>
+        <v>293.49578256794751</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="3">
         <v>2021</v>
@@ -922,58 +3012,106 @@
         <v>2023</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>3811</v>
+      </c>
+      <c r="C9" s="2">
+        <v>4043</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4439</v>
+      </c>
+      <c r="E9" s="2">
+        <f>(C9/B9)*100</f>
+        <v>106.08764103909736</v>
+      </c>
+      <c r="F9" s="2">
+        <f>(D9/C9)*100</f>
+        <v>109.79470690081624</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>875</v>
+      </c>
+      <c r="C10" s="2">
+        <v>868</v>
+      </c>
+      <c r="D10" s="2">
+        <v>692</v>
+      </c>
+      <c r="E10" s="2">
+        <f t="shared" ref="E10:E12" si="0">(C10/B10)*100</f>
+        <v>99.2</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" ref="F10:F12" si="1">(D10/C10)*100</f>
+        <v>79.723502304147459</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>5419</v>
+      </c>
+      <c r="C11" s="2">
+        <v>6221</v>
+      </c>
+      <c r="D11" s="2">
+        <v>7416</v>
+      </c>
+      <c r="E11" s="2">
+        <f t="shared" si="0"/>
+        <v>114.79977855692934</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="1"/>
+        <v>119.20913036489311</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>1435</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1878</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1493</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>130.87108013937282</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="1"/>
+        <v>79.499467518636848</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="3">
         <v>2021</v>
@@ -985,33 +3123,58 @@
         <v>2023</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
+      <c r="B17" s="2">
+        <v>26042</v>
+      </c>
+      <c r="C17" s="2">
+        <v>24411</v>
+      </c>
+      <c r="D17" s="2">
+        <v>24917</v>
+      </c>
+      <c r="E17" s="2">
+        <f>(C17/B17)*100</f>
+        <v>93.737040165885873</v>
+      </c>
+      <c r="F17" s="2">
+        <f>(D17/C17)*100</f>
+        <v>102.0728360165499</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
+      <c r="B18" s="11">
+        <v>0.66</v>
+      </c>
+      <c r="C18" s="11">
+        <v>0.65</v>
+      </c>
+      <c r="D18" s="11">
+        <v>0.66</v>
+      </c>
+      <c r="E18" s="2">
+        <f>(C18/B18)*100</f>
+        <v>98.484848484848484</v>
+      </c>
+      <c r="F18" s="2">
+        <f>(D18/C18)*100</f>
+        <v>101.53846153846153</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>